--- a/光伏配储项目/电价数据/2026/琴江站.xlsx
+++ b/光伏配储项目/电价数据/2026/琴江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42087</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.46553</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.48709</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24584</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.12163</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.01779</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.06309000000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.06698</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.56177</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74337</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14754</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.39766</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66847</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8944800000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21811</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35274</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17023</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.04843</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31449</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41675</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.70992</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.76186</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13994</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95321</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91313</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80845</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.77103</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52028</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43185</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73451</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.91108</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9773099999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5449400000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52225</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50359</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48396</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.44579</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.52697</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.73199</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.63579</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.59527</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5657300000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5897</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49421</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.03013</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53451</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60727</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7756900000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.81016</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19493</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.43572</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14616</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8681599999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23425</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.13026</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.33826</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.09237</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11457</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67283</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00808</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.93062</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.98639</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.82716</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.38223</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.13387</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45578</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.10943</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.1591</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33555</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50232</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43957</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48832</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.23028</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80415</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.01707</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.70228</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.33292</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63063</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6709700000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47052</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.90125</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.08511</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.13705</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.18612</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.0059</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51156</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.63217</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.11847</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6182799999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.14092</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9218999999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.7807500000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.81376</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.9457300000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43821</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34306</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46007</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.60114</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.22261</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.19609</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.64452</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.75644</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.64073</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.52576</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.8021</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47931</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5295599999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47572</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5286799999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.81633</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5177</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.64039</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5269299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49873</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42864</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33261</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25726</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.03144</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13337</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03909000000000001</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.02028</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.02245</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5300199999999999</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.52436</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.45298</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.54165</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.5305299999999999</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.54945</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.42676</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.47689</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.7006100000000001</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.44157</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.54561</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.6680900000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.99734</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.89607</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.95113</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.71189</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.79326</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.6425299999999999</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1.47832</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.43271</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.70785</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.54967</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.65847</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.67045</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.7203099999999999</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.57952</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.56337</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.7216699999999999</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.44731</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10157</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19763</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26276</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14068</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01192</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05178</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.38819</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33395</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.52278</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78571</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61117</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55513</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.48777</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.5289400000000001</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.63812</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.46968</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.49789</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.61025</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.9438</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.73676</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.73262</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.08411</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8907999999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.7634500000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.9594199999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.6575800000000001</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.61768</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.38998</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.92452</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.7677200000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1.60602</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.42148</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.67989</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.48945</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.47161</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.69959</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.7085900000000001</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.83808</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.71658</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.6233500000000001</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.60315</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.43393</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.99603</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.74198</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.67923</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61529</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.8413200000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5669500000000001</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.67038</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.47794</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.46366</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.48831</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.46544</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.69104</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.99549</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.49951</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.63198</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.46774</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.49401</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.51133</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.5679500000000001</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.5143</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.5182100000000001</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.11115</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.0308</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25828</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.15252</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20378</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.40634</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7662899999999999</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.43335</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.48879</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.58068</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.8328300000000001</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43526</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.54557</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.46469</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.66023</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.66276</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.6747000000000001</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>1.4074</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.11086</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.58129</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.30195</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.81072</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.90437</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.76071</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.54635</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.08219</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.54975</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.6018600000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.53698</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.69008</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.51251</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.5043800000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.65554</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.5034</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.5274099999999999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.72282</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.52588</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.47308</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.80165</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.88128</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.48588</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.51133</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.8159099999999999</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.50326</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.6964900000000001</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.80303</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.71494</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5853700000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.8365900000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.63144</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.53267</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.9008200000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.44646</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.40315</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.17971</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26489</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.60205</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.51019</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.58373</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.49101</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.45029</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.92518</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.8316699999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.5999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.85446</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.8065399999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.55584</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.69931</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.57926</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.53104</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.5379400000000001</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.5209199999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.8404700000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.60545</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.82726</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.7049099999999999</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.70763</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.72348</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.69855</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.79042</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.5246900000000001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.53313</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.53391</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.7868099999999999</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.7861699999999999</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.29736</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.7003200000000001</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.93789</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.32411</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.75712</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.9645900000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.9047000000000001</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.57968</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.6746599999999999</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.8176599999999999</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.43347</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.75046</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.49209</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.49091</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.50303</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.45718</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13616</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.03583</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.07378</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01078</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.007030000000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02669</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.007480000000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.05746</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13607</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03258</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.52478</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.43446</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.54516</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.51337</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.53851</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.63363</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.58438</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.46587</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.64735</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.54286</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.6263500000000001</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.86548</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.6818500000000001</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.63819</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.68923</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.66135</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.8486699999999999</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.83121</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.81645</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.82865</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.52377</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.47997</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.47356</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.56008</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.5558200000000001</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.61134</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.5297200000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.47211</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.14856</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.46877</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.8944299999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.7330800000000001</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.5966699999999999</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.5884299999999999</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.6264400000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.45969</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.57313</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.50848</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.6168400000000001</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.54876</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.49639</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.48629</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.47838</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.48424</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.85157</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.57145</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.59497</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.44548</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.47362</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.45934</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25952</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18864</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18325</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.20228</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2171</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24553</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.8069500000000001</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.47569</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.43335</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.79611</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.46393</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.53718</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.44269</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.48081</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.5358099999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.88691</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.52859</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.5388500000000001</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.48956</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.49415</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.65884</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.49677</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.50548</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.47148</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.6295499999999999</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.5722999999999999</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.58627</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.5086000000000001</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.06023</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.05509</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.5664600000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.48377</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.59235</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.52703</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.47514</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.49864</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.42333</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.45894</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.46543</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.46732</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.49602</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.6244299999999999</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.5657300000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.54042</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.45979</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.52174</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.2158</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.51466</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.76275</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.45826</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.59645</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5666599999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.52419</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.56224</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.5059900000000001</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5990800000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26734</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.26229</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.73214</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.68021</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.46514</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.46973</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.57637</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.47223</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46954</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.66889</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.56589</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.49382</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.5191</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68547</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.56009</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.47148</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.55047</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5317000000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.80079</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.46987</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.62887</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>1.25722</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.59385</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.51217</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.44459</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.51084</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.75248</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.7226399999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.57004</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.81141</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.52338</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.53295</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.61324</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.73712</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.69231</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.49189</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.47994</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.48328</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.70423</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.71108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.7913</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.49965</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.7108099999999999</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.71236</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.7024400000000001</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.75071</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.84673</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.81214</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.7196900000000001</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.58417</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.48131</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.43621</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.46178</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.6040399999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.48427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.46206</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.45971</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.41436</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.47066</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.45895</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.50556</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.6028300000000001</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.55462</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.46468</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.43911</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.47801</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.8454700000000001</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.48027</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.6941799999999999</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.6134700000000001</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.44292</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.6167899999999999</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.44411</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.6511699999999999</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.85733</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.66008</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.77996</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.8601</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.6652400000000001</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.43201</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.46902</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1.39392</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.51359</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.52535</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.51124</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.4881</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.49042</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.5305</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.47784</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.5226900000000001</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.47807</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.51502</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.50434</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.52591</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.47135</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.49054</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.40777</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.46328</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.45728</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.44193</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.43224</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.48212</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.47826</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.43102</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.53252</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.5962499999999999</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.55655</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.54959</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.70038</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.50605</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.54099</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.73739</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.7627200000000001</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.66816</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.83746</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.67495</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.42185</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.47555</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.49359</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.43529</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.49267</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.49155</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.44226</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.60981</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.44123</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.43897</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.57275</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.44834</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.46234</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.44037</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.46363</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5325700000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.04392</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.23024</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.06156</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15964</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21917</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25311</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50475</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.27798</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.52699</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.4396600000000001</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.48399</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.6165499999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.78059</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.94063</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.8124199999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.75266</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.7103700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7408400000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.10078</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.9169299999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.02069</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.25582</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5969099999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.73468</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.99513</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.73783</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.69672</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.48426</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.92112</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.21168</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.01417</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.60602</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.67801</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.68386</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.62688</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.66425</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.67886</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.61782</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.6134500000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.5745399999999999</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.7127</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.6007100000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.6096900000000001</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.7053400000000001</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.66185</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.68862</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.68402</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.90738</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.86138</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.27923</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.02057</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.8280599999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.9957999999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.53504</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.4959</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.56704</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.63207</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.51506</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.54895</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.55535</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.69443</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.6155700000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.50364</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6565599999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71248</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.19856</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.63485</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.52218</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.44115</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.6324299999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.61794</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.6334500000000001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.53731</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.66311</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.48945</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.71387</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.74041</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.9392200000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.03354</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.04276</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.18685</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.74137</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.69616</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.67957</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.24259</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8486</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.70262</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.75282</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.9418200000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.97184</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.9298099999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.89803</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.88635</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.6747000000000001</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.15874</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.71673</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.7687</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.82836</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.51489</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.79757</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.6323300000000001</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.96669</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.69729</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.71233</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.6245499999999999</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.59722</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.5512899999999999</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.44064</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="V134" t="n">
+        <v>1.40211</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.56669</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.6854199999999999</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.68049</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.56886</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.45996</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.45583</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.60387</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.48001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.59229</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.49137</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.41392</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.48339</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.55757</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02669</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.29861</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.54648</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.48117</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.73591</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.02686</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03583</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.49606</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.46373</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.55659</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.60303</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.47101</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.72492</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.78372</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.5199600000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.7977300000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.4885</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.63566</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.8315900000000001</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.86095</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.7767999999999999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.5774900000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.76249</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.7275700000000001</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.6088899999999999</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.70256</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.92211</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.58025</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.87903</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.94928</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.91557</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.78454</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.7140700000000001</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.02545</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.8423200000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7781399999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.8364</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.7872100000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.81229</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.8477899999999999</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.41472</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.61591</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1.34909</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.33511</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.84665</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1.38065</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.7423200000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.8468300000000001</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1.27965</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.80508</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.8249299999999999</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.7313500000000001</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.8140599999999999</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.82528</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.8365</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1.24606</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.84772</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1.24216</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.31041</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.8926499999999999</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.68657</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.77146</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.32525</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.61526</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.53574</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.49154</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.14137</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.49356</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.17893</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.18844</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.5132000000000001</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.02404</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25792</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.15928</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25677</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01152</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27694</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.13573</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.47888</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.47538</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.51095</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.57236</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.49293</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.67392</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.5621900000000001</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.65335</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.66404</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.5530900000000001</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.70348</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.5797</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.6809700000000001</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.6139</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.79588</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.82402</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.7948500000000001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.67977</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.68159</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.63566</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.58251</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.66404</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.89039</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.9148500000000001</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.59823</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.8457100000000001</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.54083</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.84714</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.67322</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.5707300000000001</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.57012</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.51113</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.50941</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.5166499999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1.12328</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.69745</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.68751</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1.17333</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.59733</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.55604</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.5681499999999999</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.05432</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.21285</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1.17539</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.1754</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="V136" t="n">
+        <v>1.16994</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.5963999999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>1.19602</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.16177</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1.16312</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.6711</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.21354</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.21252</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.2002</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.81686</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.08563999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00092</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01436</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03775</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00253</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03564</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20775</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1.1847</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.46021</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.51262</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.53126</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.49301</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.55111</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8189299999999999</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.48161</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.57157</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.48317</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.48963</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.49493</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.5821900000000001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.7326900000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.83429</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.83611</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.9762799999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.66699</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.9255399999999999</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.85481</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.8763</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.47775</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.8444299999999999</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.7990900000000001</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.52433</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.37187</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1.55206</v>
+      </c>
+      <c r="V137" t="n">
+        <v>1.39309</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.51986</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1.49253</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.37013</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1.42347</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1.51547</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.52728</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.9726699999999999</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.5872200000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>1.38787</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.87661</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.97258</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87251</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03385</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.15891</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00317</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.59787</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.45324</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.51688</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.49296</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.59934</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.68121</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.06045</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.58208</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.92288</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.92113</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.92525</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.02171</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.48845</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.48785</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.5669299999999999</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.56677</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.9469</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.59075</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.4953</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.58011</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1.02416</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.8084199999999999</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.83458</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.7676799999999999</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.96001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.60272</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.61534</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.69921</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1.19711</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.75603</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.8580099999999999</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.74014</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.83562</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.8445499999999999</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1.44986</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.01607</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.91869</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1.00111</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.16644</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.82065</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.86975</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5841799999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.53046</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.04962</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.10466</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.08993999999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24666</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25992</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.44155</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45837</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.52555</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.52583</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.50824</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.53063</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5111600000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.02532</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.75083</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.65696</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.97133</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.62061</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.8406</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.82631</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.7107599999999999</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>1.13378</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.53306</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.58253</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.53983</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.5727100000000001</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.55014</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.71975</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.65739</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6704199999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.6155499999999999</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.6054299999999999</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.59008</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.54734</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.5324800000000001</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.53285</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.50774</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.43162</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.53301</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.49314</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.49043</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.4911</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.48631</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.48438</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.48445</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.5126799999999999</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.53187</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.5145700000000001</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.53261</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.49379</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.51876</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.8687699999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5578200000000001</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.53945</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.55777</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.51785</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.34973</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.98952</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.53152</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.44215</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.90289</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6658999999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.6329199999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.9479099999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.62928</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.19058</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82859</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.89958</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.43418</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.37864</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.95869</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7172999999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.92977</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.56721</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45822</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.8066599999999999</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.60682</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.49336</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.60148</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.52834</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.52397</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.5164299999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7018799999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.6169199999999999</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.59209</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.56633</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.48762</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.55025</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.54343</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.54142</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.53354</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.5051100000000001</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.48544</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.48795</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.48783</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.49808</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.49381</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.49182</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.5521699999999999</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.55823</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.6614</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.57961</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.44671</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.47693</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.43917</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.48424</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.45029</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.48219</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.50274</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.45703</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.45783</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.50568</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.54702</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.83988</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.85758</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.6732400000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.23017</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.23442</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.71029</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.70231</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.14396</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.64652</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.15158</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.43466</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80225</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.73597</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.84227</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.54403</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.7340399999999999</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.65865</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.57239</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.50348</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.50483</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.5172599999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.48083</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.52339</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.43888</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.42884</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.5234800000000001</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.5378200000000001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.52762</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.48618</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.47345</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.42096</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1.44856</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.49814</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.50793</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.53326</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.59527</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.5969500000000001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.46438</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.46586</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.44365</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.50913</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.50338</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.6253200000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.47732</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23664</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20535</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.18747</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24366</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03238000000000001</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16144</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02687</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01808</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16212</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18582</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03201</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.04995</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.22971</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24747</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.44587</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.45977</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.50169</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.6449199999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.47514</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.53559</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.50552</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.79232</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.52281</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.64081</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.6854600000000001</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.56733</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.53051</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.56743</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.55088</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.64758</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.48283</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.5421</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.50886</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.5424800000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.57743</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.58938</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.70901</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.60099</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.56924</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.47822</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.48439</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.5236799999999999</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.48878</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.48903</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.4852</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.48364</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.47922</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.47929</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.47333</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.46231</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.46991</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.4753500000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.4679700000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.10563</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27218</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.46339</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44789</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.49032</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.41347</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.49257</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.45626</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.48106</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.48139</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.46524</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5589500000000001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.53243</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.52174</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.43823</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.45818</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.45748</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61373</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.65251</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.49123</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.49053</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.49209</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.52811</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.48838</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.47598</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.46572</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.46825</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.45303</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17682</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14646</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23698</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04731</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13357</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17681</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22788</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27066</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15775</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21926</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00136</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20199</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26421</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27471</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47105</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.41549</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.49732</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.60224</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.55163</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.51989</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.48377</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.49238</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.60165</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.48785</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.51339</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.48399</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.46062</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.46124</v>
       </c>
     </row>
   </sheetData>
